--- a/servers/maze_main_server/conf.d/data/maze_shop_area_v8【迷宫-商店-刷怪区域id对应商店】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_shop_area_v8【迷宫-商店-刷怪区域id对应商店】.xlsx
@@ -1,35 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D17D4C-7A9D-44E5-8A03-9C9747DB56F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59641F3E-8B29-496C-926E-885A53E6C107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{814E0E55-A886-40A1-8333-E4B921F33C57}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_shop_area_v8" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -460,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC20F1CA-48B7-48C4-AB53-FA4734F5DBBE}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
@@ -509,101 +498,46 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>0</v>
+        <v>30001</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2">
-        <v>160</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>10001</v>
+        <v>40001</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>20001</v>
+        <v>50001</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
       </c>
       <c r="C7" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>30001</v>
+        <v>50002</v>
       </c>
       <c r="B8" s="2">
         <v>1</v>
       </c>
       <c r="C8" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>40001</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>50001</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>50002</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2">
         <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>60001</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>60002</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_shop_area_v8【迷宫-商店-刷怪区域id对应商店】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_shop_area_v8【迷宫-商店-刷怪区域id对应商店】.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A986C3A-2FB8-43D4-A86F-D2D0328996D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D17D4C-7A9D-44E5-8A03-9C9747DB56F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{814E0E55-A886-40A1-8333-E4B921F33C57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{814E0E55-A886-40A1-8333-E4B921F33C57}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_shop_area_v8" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -51,16 +62,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>INT_K</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S_C</t>
   </si>
 </sst>
 </file>
@@ -450,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC20F1CA-48B7-48C4-AB53-FA4734F5DBBE}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
@@ -459,20 +469,20 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -499,46 +509,101 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>30001</v>
+        <v>0</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2">
-        <v>3</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>40001</v>
+        <v>10001</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>50001</v>
+        <v>20001</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
       </c>
       <c r="C7" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
+        <v>30001</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>40001</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>50001</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>50002</v>
       </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
         <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>60001</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>60002</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_shop_area_v8【迷宫-商店-刷怪区域id对应商店】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_shop_area_v8【迷宫-商店-刷怪区域id对应商店】.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59641F3E-8B29-496C-926E-885A53E6C107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D17D4C-7A9D-44E5-8A03-9C9747DB56F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{814E0E55-A886-40A1-8333-E4B921F33C57}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_shop_area_v8" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -449,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC20F1CA-48B7-48C4-AB53-FA4734F5DBBE}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
@@ -498,46 +509,101 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>30001</v>
+        <v>0</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2">
-        <v>3</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>40001</v>
+        <v>10001</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>50001</v>
+        <v>20001</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
       </c>
       <c r="C7" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
+        <v>30001</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>40001</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>50001</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>50002</v>
       </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
         <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>60001</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>60002</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
